--- a/artfynd/A 24984-2025 artfynd.xlsx
+++ b/artfynd/A 24984-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY8"/>
+  <dimension ref="A1:AY14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,12 +678,7 @@
         <v>119871405</v>
       </c>
       <c r="B2" t="n">
-        <v>96198</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Godkänd. Foto (eller ljud) granskat av validerare</t>
-        </is>
+        <v>97733</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -792,61 +787,51 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120174574</v>
+        <v>120278936</v>
       </c>
       <c r="B3" t="n">
-        <v>97930</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91893</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>4660</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rävticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Inocutis rheades</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
+          <t>(Pers.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Amundshatt, Boh</t>
+          <t>Amunderöd, Boh</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>292510</v>
+        <v>292494</v>
       </c>
       <c r="R3" t="n">
-        <v>6521818</v>
+        <v>6521833</v>
       </c>
       <c r="S3" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -870,12 +855,22 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2024-10-02</t>
+          <t>2024-10-05</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2024-10-02</t>
+          <t>2024-10-05</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -891,27 +886,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Steve Daurer</t>
+          <t>Erland Svenson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Steve Daurer</t>
+          <t>Erland Svenson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120279000</v>
+        <v>120279002</v>
       </c>
       <c r="B4" t="n">
-        <v>90616</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -919,21 +909,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4660</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Rävticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Inocutis rheades</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Pers.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -941,22 +931,23 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Amunderöd, Boh</t>
+          <t>amunderöd, Boh</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>292494</v>
+        <v>292480</v>
       </c>
       <c r="R4" t="n">
-        <v>6521833</v>
+        <v>6521807</v>
       </c>
       <c r="S4" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -998,13 +989,17 @@
           <t>14:30</t>
         </is>
       </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>massor av hack</t>
+        </is>
+      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1023,61 +1018,56 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120278951</v>
+        <v>120174531</v>
       </c>
       <c r="B5" t="n">
-        <v>98001</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Mårtensröd, Boh</t>
+          <t>Amundshatt, Boh</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>292480</v>
+        <v>292567</v>
       </c>
       <c r="R5" t="n">
-        <v>6521806</v>
+        <v>6521839</v>
       </c>
       <c r="S5" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1101,22 +1091,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2024-10-05</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>15:00</t>
+          <t>2024-10-02</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2024-10-05</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>15:00</t>
+          <t>2024-10-02</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1125,34 +1105,28 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Erland Svenson</t>
+          <t>Steve Daurer</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Erland Svenson</t>
+          <t>Steve Daurer</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120279013</v>
+        <v>120278996</v>
       </c>
       <c r="B6" t="n">
-        <v>57332</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1192,10 +1166,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>292553</v>
+        <v>292522</v>
       </c>
       <c r="R6" t="n">
-        <v>6521837</v>
+        <v>6521792</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1227,7 +1201,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1237,12 +1211,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Ringhack tall</t>
+          <t>ringhack tall</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1269,61 +1243,56 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120278950</v>
+        <v>120279013</v>
       </c>
       <c r="B7" t="n">
-        <v>98001</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Mårtensröd, Boh</t>
+          <t>Amunderöd, Boh</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>292486</v>
+        <v>292553</v>
       </c>
       <c r="R7" t="n">
-        <v>6521810</v>
+        <v>6521837</v>
       </c>
       <c r="S7" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1352,7 +1321,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1362,7 +1331,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>15:30</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Ringhack tall</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1371,7 +1345,6 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1390,61 +1363,52 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120279002</v>
+        <v>101123300</v>
       </c>
       <c r="B8" t="n">
-        <v>57348</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57141</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100049</v>
+        <v>100138</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>amunderöd, Boh</t>
+          <t>Amunderöd-Ranebo, Boh</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>292480</v>
+        <v>292486</v>
       </c>
       <c r="R8" t="n">
-        <v>6521807</v>
+        <v>6521852</v>
       </c>
       <c r="S8" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1468,27 +1432,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2024-10-05</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>14:30</t>
+          <t>2022-05-24</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2024-10-05</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>14:30</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>massor av hack</t>
+          <t>2022-05-24</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1503,15 +1452,660 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>101123229</v>
+      </c>
+      <c r="B9" t="n">
+        <v>5179</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>100526</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Bronshjon</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Callidium coriaceum</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Amunderöd-Ranebo, Boh</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>292570</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6521848</v>
+      </c>
+      <c r="S9" t="n">
+        <v>25</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Tanum</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Bohuslän</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Lur</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2022-05-24</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2022-05-24</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF9" t="inlineStr"/>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>101123230</v>
+      </c>
+      <c r="B10" t="n">
+        <v>5199</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>105930</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Vågbandad barkbock</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Semanotus undatus</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Amunderöd-Ranebo, Boh</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>292570</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6521848</v>
+      </c>
+      <c r="S10" t="n">
+        <v>25</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Tanum</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Bohuslän</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Lur</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2022-05-24</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2022-05-24</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF10" t="inlineStr"/>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>120174574</v>
+      </c>
+      <c r="B11" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Amundshatt, Boh</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>292510</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6521818</v>
+      </c>
+      <c r="S11" t="n">
+        <v>5</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Tanum</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Bohuslän</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Lur</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2024-10-02</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2024-10-02</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF11" t="inlineStr"/>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>120278950</v>
+      </c>
+      <c r="B12" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Mårtensröd, Boh</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>292486</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6521810</v>
+      </c>
+      <c r="S12" t="n">
+        <v>1</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Tanum</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Bohuslän</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Lur</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2024-10-05</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2024-10-05</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF12" t="inlineStr"/>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
           <t>Erland Svenson</t>
         </is>
       </c>
-      <c r="AX8" t="inlineStr">
+      <c r="AX12" t="inlineStr">
         <is>
           <t>Erland Svenson</t>
         </is>
       </c>
-      <c r="AY8" t="inlineStr"/>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>120278951</v>
+      </c>
+      <c r="B13" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Mårtensröd, Boh</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>292480</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6521806</v>
+      </c>
+      <c r="S13" t="n">
+        <v>1</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Tanum</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Bohuslän</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Lur</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2024-10-05</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2024-10-05</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF13" t="inlineStr"/>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Erland Svenson</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Erland Svenson</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>120174535</v>
+      </c>
+      <c r="B14" t="n">
+        <v>80392</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>229497</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Korallblylav</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Parmeliella triptophylla</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Ach.) Müll.Arg.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Amundshatt, Boh</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>292567</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6521839</v>
+      </c>
+      <c r="S14" t="n">
+        <v>5</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Tanum</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Bohuslän</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Lur</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2024-10-02</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2024-10-02</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF14" t="inlineStr"/>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 24984-2025 artfynd.xlsx
+++ b/artfynd/A 24984-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY14"/>
+  <dimension ref="A1:AZ14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -784,6 +789,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119871405</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -895,6 +905,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120278936</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1015,6 +1030,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120279002</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1120,6 +1140,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120174531</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1240,6 +1265,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120278996</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1360,6 +1390,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120279013</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1461,6 +1496,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101123300</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1564,6 +1604,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101123229</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1667,6 +1712,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101123230</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1773,6 +1823,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120174574</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1889,6 +1944,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120278950</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2005,6 +2065,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120278951</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2106,8 +2171,28 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120174535</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>